--- a/aq_files/0195.xlsx
+++ b/aq_files/0195.xlsx
@@ -1,98 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>What is the main idea behind the nearest neighbor concept?</t>
-  </si>
-  <si>
-    <t>How does KNN use distance to classify a new data point?</t>
-  </si>
-  <si>
-    <t>Which distance metric is most commonly used in KNN?</t>
-  </si>
-  <si>
-    <t>Can KNN use other distance metrics besides Euclidean?</t>
-  </si>
-  <si>
-    <t>How do you determine which neighbors are “nearest”?</t>
-  </si>
-  <si>
-    <t>What role does the value of K play in identifying neighbors?</t>
-  </si>
-  <si>
-    <t>How does KNN handle ties when neighbors vote for different classes?</t>
-  </si>
-  <si>
-    <t>How does weighted voting change the influence of neighbors?</t>
-  </si>
-  <si>
-    <t>How does KNN prediction work for regression problems?</t>
-  </si>
-  <si>
-    <t>How do outliers affect nearest neighbor calculations?</t>
-  </si>
-  <si>
-    <t>How does feature scaling affect distance computation in KNN?</t>
-  </si>
-  <si>
-    <t>How do you visualize the nearest neighbors in a 2D feature space?</t>
-  </si>
-  <si>
-    <t>How does the nearest neighbor concept help in classifying borderline points?</t>
-  </si>
-  <si>
-    <t>How does the choice of distance metric affect the nearest neighbors?</t>
-  </si>
-  <si>
-    <t>How is KNN a “lazy learner” in terms of nearest neighbors?</t>
-  </si>
-  <si>
-    <t>How do you compute the Euclidean distance between two points manually?</t>
-  </si>
-  <si>
-    <t>How do you compute Manhattan distance for nearest neighbors?</t>
-  </si>
-  <si>
-    <t>How does increasing K affect bias and variance in neighbor classification?</t>
-  </si>
-  <si>
-    <t>How do you assign a new data point to a cluster using nearest neighbor logic?</t>
-  </si>
-  <si>
-    <t>How is the nearest neighbor concept used in other algorithms like k-means or anomaly detection?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +38,87 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,650 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="46.25" customWidth="1" style="2" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Practical Question</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Command/Operation</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Output</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>You accidentally deleted a critical file 3 days ago. How do you recover it using version control?</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>git log --oneline, git checkout &lt;commit&gt; -- &lt;file&gt;</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Recovered file with all previous content</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Your team member introduced a bug 5 commits ago. Find and revert only that specific change</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>git bisect start, git bisect bad, git bisect good, git revert &lt;commit&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Bug identified and reverted without losing later changes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>You need to understand why a specific line of code was written 2 months ago</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>git blame &lt;filename&gt;, git show &lt;commit&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Shows author, commit, and message for each line</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Two developers modified the same file simultaneously. Resolve the conflict while preserving both changes</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>git merge, manual conflict resolution</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Merged file with both changes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>You want to see who has made the most contributions to a specific file in the last month</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>git shortlog -sn -- &lt;filename&gt;, git log --since="1 month ago" -- &lt;filename&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>List of contributors with commit counts</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>You need to create a report of all changes made between two releases (v1.0 and v2.0)</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>git log v1.0..v2.0 --oneline, git diff v1.0..v2.0 --stat</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Complete changelog between releases</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>You want to see what changes were made yesterday across the entire project</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>git log --since="yesterday" --oneline --stat</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>List of yesterday's commits with file changes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Your team needs to implement a new feature without affecting the stable main codebase</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>git branch feature-branch, git checkout feature-branch</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Isolated branch for feature development</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>You made experimental changes that didn't work. Discard all uncommitted changes</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>git restore ., git clean -fd</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Working directory cleaned, all uncommitted changes removed</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>You need to temporarily switch to a different task while keeping current changes</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>git stash, git checkout other-branch, git stash pop</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Changes saved and restored after task switch</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>You accidentally committed to the main branch instead of a feature branch. Move that commit to a new branch</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>git branch feature-branch, git reset HEAD~1, git checkout feature-branch</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Commit moved to correct branch</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>You want to track which commit introduced a specific function in the codebase</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>git log -S"function_name" --oneline</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Shows commits where function was added/modified</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>Your team wants to enforce code review before merging changes to main branch</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>Configure protected branch in GitHub/GitLab, require pull request reviews</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Pull request requires approval before merge</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>You need to see the difference between your current working directory and the last commit</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>git diff HEAD</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>Shows all unstaged changes</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>You want to see which commits modified a specific line range in a file</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>git log -L &lt;start&gt;,&lt;end&gt;:&lt;filename&gt;</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Shows commits affecting specific lines</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>Your team needs to tag a specific commit as release version 2.0</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>git tag -a v2.0 -m "Release version 2.0", git push origin v2.0</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Tag created and pushed to remote</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>You want to verify that your local repository matches the remote repository</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>git fetch, git status, git log origin/main..HEAD</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>Shows local commits not yet pushed</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>You need to find out who deleted a specific file and when</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>git log --diff-filter=D -- &lt;filename&gt;</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Shows commit where file was deleted</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>Your team wants to automate deployment when code is pushed to main branch</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>Create GitHub Actions workflow (.github/workflows/deploy.yml)</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>Automatic deployment on push to main</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>Version Control Purpose</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>You want to measure team productivity using version control metrics</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>git log --author="Developer" --since="month" --oneline | wc -l</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>Commit count per developer over time</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>